--- a/arquivos/facilidades_tecnologia_prioridade.xlsx
+++ b/arquivos/facilidades_tecnologia_prioridade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\NFV 3.0\arquivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao nfv automatico\NEW_NFV\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97CE505-9365-4A26-8783-4B05393EF4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6B9AC8-3924-4DBB-B3F3-044A0F9ED02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="47">
   <si>
     <t>4G</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>VIRTUA HFC</t>
+  </si>
+  <si>
+    <t>VIRTUA GPON</t>
   </si>
   <si>
     <t>GPON RES RESID</t>
@@ -591,7 +594,7 @@
         <v>18</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -602,13 +605,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -619,7 +622,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -636,10 +639,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -656,10 +659,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -676,7 +679,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -693,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -710,7 +713,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -747,7 +750,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -872,7 +875,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -906,7 +909,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
         <v>18</v>
